--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e-constrained CareTeam profile derived from US Core CareTeam.
+    <t>314e-constrained CareTeam profile derived from QI-Core CareTeam.
 This profile applies 314e-defined extensions and uses 314e datatype profiles
 where applicable.</t>
   </si>
@@ -116,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam</t>
+    <t>http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careteam</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -587,11 +587,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
-    <t>Who care team is for</t>
+    <t>(QI) Who the care team is for.</t>
   </si>
   <si>
     <t>Identifies the patient or group whose intended care is handled by the team.</t>
@@ -607,7 +607,7 @@
     <t>CareTeam.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -716,7 +716,7 @@
     <t>CareTeam.participant.role</t>
   </si>
   <si>
-    <t>Type of involvement</t>
+    <t>(QI) Type of involvement</t>
   </si>
   <si>
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary care physician", "Trained social worker counselor", "Caregiver", etc.</t>
@@ -743,11 +743,11 @@
     <t>CareTeam.participant.member</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
-    <t>Who is involved</t>
+    <t>(QI) Who is involved</t>
   </si>
   <si>
     <t>The specific person or organization who is participating/expected to participate in the care team.</t>
@@ -769,7 +769,7 @@
     <t>CareTeam.participant.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -812,7 +812,7 @@
     <t>CareTeam.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careteam-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careteam-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
